--- a/human_resources_forms/014_workforce_engagement_questionnaire--human_resources_forms.xlsx
+++ b/human_resources_forms/014_workforce_engagement_questionnaire--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'non-binary',_'value':_'non-binary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Binary', 'value': 'non-binary'}</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'prefer_not_to_say',_'value':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Prefer Not To Say', 'value': 'prefer_not_to_say'}</t>
+          <t>Prefer Not To Say</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very good', 'value': 'very_good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 'poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor',_'value':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very poor', 'value': 'very_poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
